--- a/02_加值成品/八上/八上1-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上1-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上1-1 科學的態度與方法　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二上學期 八上1-1 科學的態度與方法　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>科學方法通常從哪一步開始？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>觀察</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>公尺(m)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>下一位</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>觀察現象才引發問題</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>SI 制中長度的單位是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>植物生長高度</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>公尺(m)</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>降低隨機誤差</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>應變變因</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>國際基本量</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>SI 制中質量的單位是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>操縱變因</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>下一位</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>公斤(kg)</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>控制變因</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>基本量</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>SI 制中時間的單位是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>秒(s)</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>下一位</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>公尺(m)</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>降低隨機誤差</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>基本量</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>實驗中刻意改變的變因稱為？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>下一位</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>公斤(kg)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>公尺(m)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>操縱變因</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>即自變項</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>隨之改變、被測量的變因稱為？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>觀察</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>植物生長高度</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>應變變因</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>下一位</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>即依變項</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>為求公平而保持不變的變因？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>操縱變因</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>公斤(kg)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>控制變因</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>其他條件相同</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>對照組的作用是什麼？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>作為比較的基準</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>如實記錄不竄改</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>水量/土壤/溫度</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>陽光(照光量)</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>凸顯操縱變因效應</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>讀尺時要估到最小刻度的？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>公斤(kg)</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>降低隨機誤差</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>觀察</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>下一位</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>估計值</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>溫度的 SI 基本單位是？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>不同</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>公尺(m)</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>克耳文(K)</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>操縱變因</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>絕對溫標</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上1-1 科學的態度與方法　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二上學期 八上1-1 科學的態度與方法　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>研究「陽光影響植物生長」，操縱變因是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>陽光(照光量)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>科學具暫時性可修正</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>操縱:鹽量 應變:沸點 控制:水量與火力</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>如實記錄不竄改</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>刻意改變的量</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>承上，應變變因是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>植物生長高度</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>應變變因</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>操縱變因</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>秒(s)</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>被測量的結果</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>承上，需控制的變因舉一例？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>水量/土壤/溫度</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>0.01cm 位</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>如實記錄不竄改</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>檢查步驟並重測</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>保持相同</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>最小刻度 0.1cm 的尺，長度應記錄到哪一位？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>導出量, m²</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>作為比較的基準</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>科學具暫時性可修正</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>0.01cm 位</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>估到下一位</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>3.50cm 有幾位有效數字？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>3 位</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>作基準比較凸顯鹽的效應</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>乙</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>秒(s)</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>末位 0 有效</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>「醣加熱會焦化」在科學方法中屬於？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>乙</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>秒(s)</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>假設</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>應變變因</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>對問題的暫時解答</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>只做一次實驗，結果可靠嗎？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>操縱變因</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>應變變因</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>公斤(kg)</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>不可靠</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>需重複多次</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>讀量筒體積時視線應對準？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>應變變因</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>操縱變因</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>凹液面最低處</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>秒(s)</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>避免視差</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>密度是基本量還是導出量？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>導出量</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>秒(s)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>公尺(m)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>不同</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>質量÷體積</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>數據與假設不符時應如何？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>操縱:鹽量 應變:沸點 控制:水量與火力</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>如實記錄不竄改</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>作為比較的基準</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>導出量, m²</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>誠實客觀</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上1-1 科學的態度與方法　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二上學期 八上1-1 科學的態度與方法　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>設計「鹽量影響水沸點」實驗，寫出三類變因</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>操縱:鹽量 應變:沸點 控制:水量與火力</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>科學具暫時性可修正</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>作為比較的基準</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>陽光(照光量)</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>完整變因設計</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何要設「不加鹽」的對照組？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>科學具暫時性可修正</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>水量/土壤/溫度</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>操縱:鹽量 應變:沸點 控制:水量與火力</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>作基準比較凸顯鹽的效應</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>對照精神</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>甲量 2.5cm、乙量 2.50cm，誰較精密？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>乙</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>導出量</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>秒(s)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>不可靠</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>估到更小一位</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>重複量同物 5 次取平均，目的是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>降低隨機誤差</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>操縱變因</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>不可靠</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>公尺(m)</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>提高可靠度</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>12.0cm 與 12cm 意義相同嗎？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>乙</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>觀察</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>不同</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>前者精密到 0.1</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>「這藥草能治百病」是科學主張嗎？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>凹液面最低處</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>應變變因</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>不是</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>控制變因</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>無法檢驗、過度宣稱</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>面積是基本量或導出量？單位？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>導出量, m²</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>如實記錄不竄改</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>0.01cm 位</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>操縱:鹽量 應變:沸點 控制:水量與火力</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>長度×長度</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>數據異常過大時，最先該做什麼？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>導出量, m²</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>如實記錄不竄改</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>檢查步驟並重測</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>陽光(照光量)</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>不可直接刪除</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>1.5 km 等於幾公尺？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>1500 m</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>凹液面最低處</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>下一位</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>檢查步驟並重測</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>×1000</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>科學結論為何常說「目前證據支持」？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>科學具暫時性可修正</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>作基準比較凸顯鹽的效應</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>檢查步驟並重測</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>如實記錄不竄改</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>科學本質</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八上/八上1-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上1-1_三種難度測驗卷.xlsx
@@ -1234,32 +1234,32 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>「醣加熱會焦化」在科學方法中屬於？</t>
+          <t>「糖加熱會焦化」在科學方法中屬於？</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>乙</t>
+          <t>植物生長高度</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>秒(s)</t>
+          <t>導出量</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
+          <t>觀察</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
           <t>假設</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>應變變因</t>
-        </is>
-      </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">

--- a/02_加值成品/八上/八上1-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上1-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>觀察現象才引發問題</t>
+          <t>觀察現象才引發問題：科學探究通常先觀察到某個現象，才會進一步引發想要探究的問題</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>國際基本量</t>
+          <t>國際基本量：國際單位制規定長度的基本單位是公尺，符號寫作m</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>基本量</t>
+          <t>基本量：國際單位制規定質量的基本單位是公斤，符號寫作kg</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>基本量</t>
+          <t>基本量：國際單位制規定時間的基本單位是秒，符號寫作s</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>即自變項</t>
+          <t>即自變項：實驗中由研究者刻意改變的那個變因，稱為操縱變因，又稱自變項</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>即依變項</t>
+          <t>即依變項：隨著操縱變因改變而跟著變化、需要被測量記錄的結果，稱為應變變因</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>其他條件相同</t>
+          <t>其他條件相同：除了操縱變因以外，其他必須保持相同以確保比較公平的變因，稱為控制變因</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>凸顯操縱變因效應</t>
+          <t>凸顯操縱變因效應：對照組沒有施加操縱變因，作為比較的基準，才能凸顯出操縱變因真正造成的效應</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>估計值</t>
+          <t>估計值：測量讀數時要在最小刻度之下再合理估讀一位，這一位稱為估計值</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>絕對溫標</t>
+          <t>絕對溫標：國際單位制規定溫度的基本單位是克耳文，是一種絕對溫標</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>刻意改變的量</t>
+          <t>刻意改變的量：這個實驗中研究者刻意改變的是陽光的照射量，所以陽光就是操縱變因</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>被測量的結果</t>
+          <t>被測量的結果：植物長高的程度是隨陽光多寡而改變、需要測量記錄的結果，所以是應變變因</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>保持相同</t>
+          <t>保持相同：除了陽光之外，水量、土壤種類、溫度等都必須保持相同，才能確保只有陽光造成生長差異</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>估到下一位</t>
+          <t>估到下一位：讀數時要在最小刻度0.1cm之下再估讀一位，也就是要記錄到0.01cm這一位</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>末位 0 有效</t>
+          <t>末位 0 有效：3、5、0這三個數字都是測量得到的結果，末位的0也算有效數字，所以共有3位</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>對問題的暫時解答</t>
+          <t>對問題的暫時解答：這句話是還沒被驗證、對問題提出的暫時性解答，屬於假設</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>需重複多次</t>
+          <t>需重複多次：只做一次實驗容易受到偶然誤差影響，必須重複做多次才能提高結果的可靠度</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>避免視差</t>
+          <t>避免視差：讀取量筒刻度時，視線要與凹液面的最低處保持水平，才能避免因視角不同造成的讀數誤差(視差)</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>質量÷體積</t>
+          <t>質量÷體積：密度是由質量和體積這兩個基本量計算組合而成的，屬於導出量</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>誠實客觀</t>
+          <t>誠實客觀：科學研究要求誠實記錄真實數據，即使與原本的假設不符也不能竄改，這是科學的基本態度</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>完整變因設計</t>
+          <t>完整變因設計：這個實驗中，刻意改變的鹽量是操縱變因，被測量的沸點是應變變因，而水量、火力大小等則必須保持相同，屬於控制變因</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>對照精神</t>
+          <t>對照精神：留一組不加鹽當作對照組，可以拿來和加鹽的各組比較，才能確定沸點的改變真的是鹽造成的</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>估到更小一位</t>
+          <t>估到更小一位：乙的讀數多了一位小數(0.50)，代表估讀到更小的位數，測量比甲更精密</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>提高可靠度</t>
+          <t>提高可靠度：多次測量取平均值，可以抵消每次測量時偶然發生的隨機誤差，讓結果更接近真實值、更可靠</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>前者精密到 0.1</t>
+          <t>前者精密到 0.1：12.0cm多寫了小數點後一位0，代表測量精密到0.1公分，和只寫12cm(精密到1公分)所代表的精密程度不同</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>無法檢驗、過度宣稱</t>
+          <t>無法檢驗、過度宣稱：科學主張必須能被具體驗證或否證，「治百病」這種空泛誇大、無法用實驗檢驗的說法不算科學主張</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>長度×長度</t>
+          <t>長度×長度：面積是由長度這個基本量自己相乘組合出來的，屬於導出量，單位是m²</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>不可直接刪除</t>
+          <t>不可直接刪除：發現異常數據時，應該先檢查實驗步驟是否出錯、再重新測量確認，不能未經查證就直接刪除這筆數據</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>×1000</t>
+          <t>×1000：1公里等於1000公尺，1.5乘以1000等於1500公尺</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>科學本質</t>
+          <t>科學本質：科學結論是根據目前掌握的證據所得出的最佳解釋，未來若有新證據出現，結論隨時可能被修正，這正是科學具有暫時性的本質</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八上/八上1-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上1-1_三種難度測驗卷.xlsx
@@ -1204,17 +1204,17 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>作基準比較凸顯鹽的效應</t>
+          <t>導出量</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>乙</t>
+          <t>秒(s)</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>秒(s)</t>
+          <t>控制變因</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>凹液面最低處</t>
+          <t>作為比較的基準</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>下一位</t>
+          <t>植物生長高度</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>檢查步驟並重測</t>
+          <t>公斤(kg)</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
